--- a/ABTA-System/Data/NewMemDatabase.xlsx
+++ b/ABTA-System/Data/NewMemDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Fastwork\Customer\ABTA\ABTA-System\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F78743-A70F-4FC3-8ACD-A02ABA709F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4E73D2-D457-43A7-8C33-4308C9BEE163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4E62CD03-FB27-40C9-B490-48A30120C3FE}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
   <si>
     <t>ที่อยู่อีเมล</t>
   </si>
@@ -325,6 +325,30 @@
   </si>
   <si>
     <t>จำนวนเงิน</t>
+  </si>
+  <si>
+    <t>Cakepuarknomsod2@gmail.com</t>
+  </si>
+  <si>
+    <t>0808026677</t>
+  </si>
+  <si>
+    <t>3-001</t>
+  </si>
+  <si>
+    <t>PK Residence</t>
+  </si>
+  <si>
+    <t>18/3 ถนนเทศบาล 46 ตำบลวารินชำราบ อำเภอวารินชำราบ จังหวัดอุบลราชธานี 34190</t>
+  </si>
+  <si>
+    <t>เพชญเกล้า จำปารัตน์</t>
+  </si>
+  <si>
+    <t>บุณยาพร อรุนยะเดช</t>
+  </si>
+  <si>
+    <t>M001</t>
   </si>
 </sst>
 </file>
@@ -854,22 +878,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{809A2A7A-CEA4-4090-82B5-AC4F6EF40CF9}">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" customWidth="1"/>
     <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29" customWidth="1"/>
     <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="74.85546875" customWidth="1"/>
     <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" customWidth="1"/>
+    <col min="10" max="10" width="27.5703125" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" customWidth="1"/>
+    <col min="12" max="12" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="66.85546875" customWidth="1"/>
     <col min="14" max="14" width="29.42578125" customWidth="1"/>
     <col min="15" max="15" width="34.42578125" customWidth="1"/>
     <col min="16" max="16" width="69" customWidth="1"/>
@@ -1209,6 +1233,62 @@
         <v>45</v>
       </c>
     </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>46224.416666666664</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="4">
+        <v>808026677</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1347600018247</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="N7" s="14"/>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="R7" s="9">
+        <v>244551.625</v>
+      </c>
+      <c r="S7" s="9">
+        <v>244551.79166666666</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{03CD33D4-0FC6-4FE6-ACD4-48614D4041E4}"/>
@@ -1216,6 +1296,7 @@
     <hyperlink ref="B4" r:id="rId3" xr:uid="{C2BF0BEE-9E55-4301-96E6-945B48B3E77E}"/>
     <hyperlink ref="B5" r:id="rId4" xr:uid="{5655DBB8-FD38-49A3-9CA2-A44332C1F6CC}"/>
     <hyperlink ref="B6" r:id="rId5" xr:uid="{13E6A275-AA3E-4734-A693-2526E5294827}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{EC58BA91-01A5-4071-95E8-B2F3E2377B46}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1226,7 +1307,7 @@
   <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="35.42578125" customWidth="1"/>
@@ -1237,6 +1318,9 @@
     <col min="9" max="9" width="20.85546875" customWidth="1"/>
     <col min="10" max="10" width="16.28515625" customWidth="1"/>
     <col min="11" max="11" width="15.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1274,7 +1358,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>23</v>
       </c>
@@ -1309,7 +1393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>242091</v>
       </c>
@@ -1344,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>242093</v>
       </c>
@@ -1414,7 +1498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>242093</v>
       </c>
@@ -1449,18 +1533,42 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>46224</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46224.416666666664</v>
+      </c>
       <c r="C7" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="20" t="s">
         <v>84</v>
       </c>
       <c r="E7" s="22">
         <v>500</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="F7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>244551.625</v>
+      </c>
+      <c r="J7" s="10">
+        <v>244714</v>
+      </c>
+      <c r="K7" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C8" s="19" t="s">
         <v>31</v>
       </c>
@@ -1471,7 +1579,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C9" s="17" t="s">
         <v>2</v>
       </c>
@@ -1482,7 +1590,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C10" s="17" t="s">
         <v>2</v>
       </c>
@@ -1493,7 +1601,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C11" s="17" t="s">
         <v>87</v>
       </c>
@@ -1504,7 +1612,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C12" s="17" t="s">
         <v>87</v>
       </c>
@@ -1515,7 +1623,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C13" s="17" t="s">
         <v>87</v>
       </c>

--- a/ABTA-System/Data/NewMemDatabase.xlsx
+++ b/ABTA-System/Data/NewMemDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Fastwork\Customer\ABTA\ABTA-System\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB4E73D2-D457-43A7-8C33-4308C9BEE163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2793354F-CF36-4727-9914-E3FB6C482E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4E62CD03-FB27-40C9-B490-48A30120C3FE}"/>
+    <workbookView xWindow="7800" yWindow="2760" windowWidth="21600" windowHeight="11835" xr2:uid="{4E62CD03-FB27-40C9-B490-48A30120C3FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Member" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="103">
   <si>
     <t>ที่อยู่อีเมล</t>
   </si>
@@ -965,7 +965,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>46222.417170833331</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46222.417170833331</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46222.417170833331</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="51.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>46222.417170833331</v>
       </c>
@@ -1179,9 +1179,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46222.417170833331</v>
+        <v>46222.417175925926</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>76</v>
@@ -1252,8 +1252,8 @@
       <c r="F7" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G7" s="4">
-        <v>808026677</v>
+      <c r="G7" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>99</v>
